--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487461_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487461_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.9426</v>
+        <v>4.9126</v>
       </c>
       <c r="E2" t="n">
-        <v>2.0198</v>
+        <v>2.2839</v>
       </c>
       <c r="F2" t="n">
-        <v>2.9227</v>
+        <v>2.6287</v>
       </c>
       <c r="G2" t="n">
         <v>3.8364</v>
@@ -610,13 +610,13 @@
         <v>2.546</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5762</v>
+        <v>0.5462</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.31</v>
+        <v>-0.0459</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8862</v>
+        <v>0.5921</v>
       </c>
       <c r="V2" t="n">
         <v>-0.0576</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1674</v>
+        <v>2.5209</v>
       </c>
       <c r="E3" t="n">
-        <v>1.4614</v>
+        <v>1.5208</v>
       </c>
       <c r="F3" t="n">
-        <v>0.706</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
         <v>4.3128</v>
@@ -688,13 +688,13 @@
         <v>2.546</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1845</v>
+        <v>0.1689</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6840000000000001</v>
+        <v>-0.6246</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4995</v>
+        <v>0.7935</v>
       </c>
       <c r="V3" t="n">
         <v>-2.5484</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Q. HUANG</t>
+          <t>N. FUENTES PRADO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5228</v>
+        <v>0.9665</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.4763</v>
+        <v>1.2294</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9991</v>
+        <v>-0.2629</v>
       </c>
       <c r="G4" t="n">
-        <v>4.5584</v>
+        <v>-0.0625</v>
       </c>
       <c r="H4" t="n">
-        <v>1.9663</v>
+        <v>0.0687</v>
       </c>
       <c r="I4" t="n">
-        <v>2.5921</v>
+        <v>-0.1313</v>
       </c>
       <c r="J4" t="n">
-        <v>5.1314</v>
+        <v>0.4083</v>
       </c>
       <c r="K4" t="n">
-        <v>1.8934</v>
+        <v>0.4083</v>
       </c>
       <c r="L4" t="n">
-        <v>3.238</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.573</v>
+        <v>-0.4708</v>
       </c>
       <c r="N4" t="n">
-        <v>0.07290000000000001</v>
+        <v>-0.3396</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.6459</v>
+        <v>-0.1313</v>
       </c>
       <c r="P4" t="n">
-        <v>-4.3087</v>
+        <v>0.3917</v>
       </c>
       <c r="Q4" t="n">
-        <v>-6.8547</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.546</v>
+        <v>0.3917</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6106</v>
+        <v>0.362</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.1286</v>
+        <v>0.5458</v>
       </c>
       <c r="U4" t="n">
-        <v>0.518</v>
+        <v>-0.1838</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8837</v>
+        <v>0.2754</v>
       </c>
       <c r="W4" t="n">
-        <v>2.3756</v>
+        <v>0.2754</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.492</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>N. FUENTES PRADO</t>
+          <t>Q. HUANG</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5037</v>
+        <v>0.8846000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8201000000000001</v>
+        <v>-0.0076</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3164</v>
+        <v>0.8922</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.0625</v>
+        <v>4.5584</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0687</v>
+        <v>1.9663</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1313</v>
+        <v>2.5921</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4083</v>
+        <v>5.1314</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4083</v>
+        <v>1.8934</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>3.238</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.4708</v>
+        <v>-0.573</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3396</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1313</v>
+        <v>-0.6459</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3917</v>
+        <v>-4.3087</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-6.8547</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3917</v>
+        <v>2.546</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1008</v>
+        <v>-0.2488</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1364</v>
+        <v>-0.6599</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2373</v>
+        <v>0.4111</v>
       </c>
       <c r="V5" t="n">
-        <v>0.2754</v>
+        <v>0.8837</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2754</v>
+        <v>2.3756</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.492</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. RODRÍGUEZ BLANCO</t>
+          <t>P. BADDINI GABRIOTTI RODRIGUES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.07539999999999999</v>
+        <v>0.3877</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1359</v>
+        <v>0.8062</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0605</v>
+        <v>-0.4185</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.1588</v>
+        <v>0.8599</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.0731</v>
+        <v>2.2188</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0857</v>
+        <v>-1.3589</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1017</v>
+        <v>1.9942</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0612</v>
+        <v>2.5552</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0404</v>
+        <v>-0.5610000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2604</v>
+        <v>-1.1344</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1344</v>
+        <v>-0.3364</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1261</v>
+        <v>-0.7979000000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>0.5875</v>
+        <v>0.7834</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R6" t="n">
-        <v>0.5875</v>
+        <v>1.7626</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5042</v>
+        <v>-0.039</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2376</v>
+        <v>-0.2088</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2666</v>
+        <v>0.1698</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-1.2166</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0776</v>
+        <v>-0.0077</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.4231</v>
+        <v>-1.4066</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3455</v>
+        <v>1.3989</v>
       </c>
       <c r="G7" t="n">
         <v>0.1272</v>
@@ -1000,13 +1000,13 @@
         <v>2.546</v>
       </c>
       <c r="S7" t="n">
-        <v>1.0325</v>
+        <v>1.1025</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3723</v>
+        <v>0.3888</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6602</v>
+        <v>0.7137</v>
       </c>
       <c r="V7" t="n">
         <v>-1.8249</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. BADDINI GABRIOTTI RODRIGUES</t>
+          <t>M. RODRÍGUEZ BLANCO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0786</v>
+        <v>-0.1022</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6874</v>
+        <v>-0.1359</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.766</v>
+        <v>0.0338</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8599</v>
+        <v>-0.1588</v>
       </c>
       <c r="H8" t="n">
-        <v>2.2188</v>
+        <v>-0.0731</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.3589</v>
+        <v>-0.0857</v>
       </c>
       <c r="J8" t="n">
-        <v>1.9942</v>
+        <v>0.1017</v>
       </c>
       <c r="K8" t="n">
-        <v>2.5552</v>
+        <v>0.0612</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5610000000000001</v>
+        <v>0.0404</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.1344</v>
+        <v>-0.2604</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3364</v>
+        <v>-0.1344</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.7979000000000001</v>
+        <v>-0.1261</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7834</v>
+        <v>0.5875</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.7626</v>
+        <v>0.5875</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5053</v>
+        <v>-0.5309</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3276</v>
+        <v>-0.2376</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1777</v>
+        <v>-0.2933</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.2166</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2166</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.5973</v>
+        <v>-1.3171</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.7569</v>
+        <v>-0.4499</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.8404</v>
+        <v>-0.8671</v>
       </c>
       <c r="G9" t="n">
         <v>-1.387</v>
@@ -1156,13 +1156,13 @@
         <v>1.1751</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7771</v>
+        <v>-0.4968</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2376</v>
+        <v>0.0694</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5395</v>
+        <v>-0.5662</v>
       </c>
       <c r="V9" t="n">
         <v>-0.6083</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.4536</v>
+        <v>-2.4301</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.4979</v>
+        <v>-3.2338</v>
       </c>
       <c r="F10" t="n">
-        <v>1.0443</v>
+        <v>0.8037</v>
       </c>
       <c r="G10" t="n">
         <v>-2.258</v>
@@ -1234,13 +1234,13 @@
         <v>0.7834</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0002</v>
+        <v>0.0237</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.594</v>
+        <v>-0.3299</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5942</v>
+        <v>0.3536</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.9708</v>
+        <v>-3.8219</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.0238</v>
+        <v>-2.9284</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.947</v>
+        <v>-0.8935</v>
       </c>
       <c r="G11" t="n">
         <v>-2.8752</v>
@@ -1312,13 +1312,13 @@
         <v>1.5668</v>
       </c>
       <c r="S11" t="n">
-        <v>1.7501</v>
+        <v>0.899</v>
       </c>
       <c r="T11" t="n">
-        <v>1.1733</v>
+        <v>0.2688</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5767</v>
+        <v>0.6302</v>
       </c>
       <c r="V11" t="n">
         <v>-2.4332</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.2302</v>
+        <v>-4.7465</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.2881</v>
+        <v>-2.6974</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.9421</v>
+        <v>-2.0491</v>
       </c>
       <c r="G12" t="n">
         <v>0.1972</v>
@@ -1390,13 +1390,13 @@
         <v>2.1543</v>
       </c>
       <c r="S12" t="n">
-        <v>0.985</v>
+        <v>0.4687</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4317</v>
+        <v>0.0223</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5533</v>
+        <v>0.4464</v>
       </c>
       <c r="V12" t="n">
         <v>-3.6498</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.347</v>
+        <v>-2.753199999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.6133</v>
+        <v>-5.019299999999999</v>
       </c>
       <c r="F13" t="n">
         <v>2.2662</v>
@@ -1468,13 +1468,13 @@
         <v>18.6054</v>
       </c>
       <c r="S13" t="n">
-        <v>1.6615</v>
+        <v>2.2555</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.4057</v>
+        <v>-0.8116000000000003</v>
       </c>
       <c r="U13" t="n">
-        <v>3.067</v>
+        <v>3.0671</v>
       </c>
       <c r="V13" t="n">
         <v>-11.1797</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D. WILLIAM</t>
+          <t>A. CORBACHO DE LA CRUZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.6498</v>
+        <v>4.0869</v>
       </c>
       <c r="E14" t="n">
-        <v>2.4912</v>
+        <v>3.3953</v>
       </c>
       <c r="F14" t="n">
-        <v>1.1586</v>
+        <v>0.6915</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.9256</v>
+        <v>-0.4003</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1912</v>
+        <v>-0.7985</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.1168</v>
+        <v>0.3982</v>
       </c>
       <c r="J14" t="n">
-        <v>1.4848</v>
+        <v>1.2039</v>
       </c>
       <c r="K14" t="n">
-        <v>1.5463</v>
+        <v>0.2858</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.0615</v>
+        <v>0.9181</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.4104</v>
+        <v>-1.6041</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.3551</v>
+        <v>-1.0843</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.0552</v>
+        <v>-0.5198</v>
       </c>
       <c r="P14" t="n">
-        <v>0.3917</v>
+        <v>2.546</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.9377</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>3.3294</v>
+        <v>2.546</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.6828</v>
+        <v>-0.2167</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5893</v>
+        <v>-0.2417</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0934</v>
+        <v>0.025</v>
       </c>
       <c r="V14" t="n">
-        <v>4.8664</v>
+        <v>2.1578</v>
       </c>
       <c r="W14" t="n">
-        <v>4.5335</v>
+        <v>2.4332</v>
       </c>
       <c r="X14" t="n">
-        <v>0.3329</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. CORBACHO DE LA CRUZ</t>
+          <t>D. WILLIAM</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.283</v>
+        <v>3.6663</v>
       </c>
       <c r="E15" t="n">
-        <v>2.7813</v>
+        <v>2.1842</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5016</v>
+        <v>1.4821</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.4003</v>
+        <v>-0.9256</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.7985</v>
+        <v>0.1912</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3982</v>
+        <v>-1.1168</v>
       </c>
       <c r="J15" t="n">
-        <v>1.2039</v>
+        <v>1.4848</v>
       </c>
       <c r="K15" t="n">
-        <v>0.2858</v>
+        <v>1.5463</v>
       </c>
       <c r="L15" t="n">
-        <v>0.9181</v>
+        <v>-0.0615</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.6041</v>
+        <v>-2.4104</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.0843</v>
+        <v>-1.3551</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.5198</v>
+        <v>-1.0552</v>
       </c>
       <c r="P15" t="n">
-        <v>2.546</v>
+        <v>0.3917</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-2.9377</v>
       </c>
       <c r="R15" t="n">
-        <v>2.546</v>
+        <v>3.3294</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.0206</v>
+        <v>-0.6662</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8557</v>
+        <v>-0.8963</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1649</v>
+        <v>0.2301</v>
       </c>
       <c r="V15" t="n">
-        <v>2.1578</v>
+        <v>4.8664</v>
       </c>
       <c r="W15" t="n">
-        <v>2.4332</v>
+        <v>4.5335</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.2754</v>
+        <v>0.3329</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. SANJURJO BOTEJARA</t>
+          <t>X. QUINTELA VALCARCEL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.1641</v>
+        <v>1.7906</v>
       </c>
       <c r="E16" t="n">
-        <v>2.482</v>
+        <v>-0.5036</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.3179</v>
+        <v>2.2943</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0279</v>
+        <v>-0.3282</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.5683</v>
+        <v>2.0263</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5962</v>
+        <v>-2.3545</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.0502</v>
+        <v>0.4635</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.0954</v>
+        <v>2.4294</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0452</v>
+        <v>-1.9659</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0781</v>
+        <v>-0.7917</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4729</v>
+        <v>-0.4031</v>
       </c>
       <c r="O16" t="n">
-        <v>0.551</v>
+        <v>-0.3886</v>
       </c>
       <c r="P16" t="n">
         <v>0.9792</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.9585</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9792</v>
+        <v>2.9377</v>
       </c>
       <c r="S16" t="n">
-        <v>1.1569</v>
+        <v>-0.4676</v>
       </c>
       <c r="T16" t="n">
-        <v>1.6485</v>
+        <v>-0.2253</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4916</v>
+        <v>-0.2423</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.6071</v>
       </c>
       <c r="W16" t="n">
-        <v>0.8837</v>
+        <v>1.2166</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.8837</v>
+        <v>0.3905</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X. QUINTELA VALCARCEL</t>
+          <t>P. SANJURJO BOTEJARA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7148</v>
+        <v>1.2993</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.0153</v>
+        <v>1.561</v>
       </c>
       <c r="F17" t="n">
-        <v>1.7301</v>
+        <v>-0.2617</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.3282</v>
+        <v>0.0279</v>
       </c>
       <c r="H17" t="n">
-        <v>2.0263</v>
+        <v>-0.5683</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.3545</v>
+        <v>0.5962</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4635</v>
+        <v>-0.0502</v>
       </c>
       <c r="K17" t="n">
-        <v>2.4294</v>
+        <v>-0.0954</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.9659</v>
+        <v>0.0452</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.7917</v>
+        <v>0.0781</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4031</v>
+        <v>-0.4729</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.3886</v>
+        <v>0.551</v>
       </c>
       <c r="P17" t="n">
         <v>0.9792</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9585</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.9377</v>
+        <v>0.9792</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.5434</v>
+        <v>0.2922</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7369</v>
+        <v>0.7275</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.8064</v>
+        <v>-0.4354</v>
       </c>
       <c r="V17" t="n">
-        <v>1.6071</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2166</v>
+        <v>0.8837</v>
       </c>
       <c r="X17" t="n">
-        <v>0.3905</v>
+        <v>-0.8837</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2431</v>
+        <v>-0.3233</v>
       </c>
       <c r="E18" t="n">
         <v>-1.4309</v>
       </c>
       <c r="F18" t="n">
-        <v>1.1878</v>
+        <v>1.1076</v>
       </c>
       <c r="G18" t="n">
         <v>1.6083</v>
@@ -1858,13 +1858,13 @@
         <v>1.3709</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2846</v>
+        <v>-0.3648</v>
       </c>
       <c r="T18" t="n">
         <v>-0.6952</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4106</v>
+        <v>0.3304</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>K. FALL</t>
+          <t>R. ESPINOZA OROZCO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4372</v>
+        <v>-0.8014</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.4712</v>
+        <v>-1.6099</v>
       </c>
       <c r="F19" t="n">
-        <v>2.034</v>
+        <v>0.8085</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.9229</v>
+        <v>-3.2158</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.6704</v>
+        <v>-1.8061</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.2525</v>
+        <v>-1.4097</v>
       </c>
       <c r="J19" t="n">
-        <v>0.7562</v>
+        <v>-1.0784</v>
       </c>
       <c r="K19" t="n">
-        <v>0.5493</v>
+        <v>-0.451</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2069</v>
+        <v>-0.6274</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.6791</v>
+        <v>-2.1375</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.2197</v>
+        <v>-1.3551</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.4594</v>
+        <v>-0.7823</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.3502</v>
+        <v>1.3709</v>
       </c>
       <c r="Q19" t="n">
-        <v>-5.8755</v>
+        <v>-1.9585</v>
       </c>
       <c r="R19" t="n">
-        <v>3.5253</v>
+        <v>3.3294</v>
       </c>
       <c r="S19" t="n">
-        <v>2.2863</v>
+        <v>-0.5061</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3935</v>
+        <v>-1.0063</v>
       </c>
       <c r="U19" t="n">
-        <v>2.6797</v>
+        <v>0.5002</v>
       </c>
       <c r="V19" t="n">
         <v>1.5495</v>
       </c>
       <c r="W19" t="n">
-        <v>3.0415</v>
+        <v>2.4332</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.492</v>
+        <v>-0.8837</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. ESPINOZA OROZCO</t>
+          <t>K. FALL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.3757</v>
+        <v>-1.5821</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.917</v>
+        <v>-2.5735</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5412</v>
+        <v>0.9915</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.2158</v>
+        <v>-1.9229</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.8061</v>
+        <v>-0.6704</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.4097</v>
+        <v>-1.2525</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.0784</v>
+        <v>0.7562</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.451</v>
+        <v>0.5493</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6274</v>
+        <v>0.2069</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.1375</v>
+        <v>-2.6791</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.3551</v>
+        <v>-1.2197</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.7823</v>
+        <v>-1.4594</v>
       </c>
       <c r="P20" t="n">
-        <v>1.3709</v>
+        <v>-2.3502</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9585</v>
+        <v>-5.8755</v>
       </c>
       <c r="R20" t="n">
-        <v>3.3294</v>
+        <v>3.5253</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.0804</v>
+        <v>1.1414</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.3133</v>
+        <v>-0.4958</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2329</v>
+        <v>1.6372</v>
       </c>
       <c r="V20" t="n">
         <v>1.5495</v>
       </c>
       <c r="W20" t="n">
-        <v>2.4332</v>
+        <v>3.0415</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.8837</v>
+        <v>-1.492</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.0335</v>
+        <v>-2.0215</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.5877</v>
+        <v>-1.7924</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.4458</v>
+        <v>-0.2291</v>
       </c>
       <c r="G21" t="n">
         <v>-0.4583</v>
@@ -2092,13 +2092,13 @@
         <v>0.5875</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0711</v>
+        <v>0.08309999999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>0.5634</v>
+        <v>0.3588</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4923</v>
+        <v>-0.2757</v>
       </c>
       <c r="V21" t="n">
         <v>-0.2754</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.375</v>
+        <v>-2.0856</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.5987</v>
+        <v>-1.4964</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7763</v>
+        <v>-0.5891999999999999</v>
       </c>
       <c r="G22" t="n">
         <v>-1.5357</v>
@@ -2170,13 +2170,13 @@
         <v>0.9792</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5639999999999999</v>
+        <v>-0.2745</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6952</v>
+        <v>-0.5928</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1312</v>
+        <v>0.3183</v>
       </c>
       <c r="V22" t="n">
         <v>-0.2754</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>3.3472</v>
+        <v>4.029199999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.266299999999999</v>
+        <v>-2.266199999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>5.6133</v>
+        <v>6.295500000000001</v>
       </c>
       <c r="G23" t="n">
         <v>-7.150600000000001</v>
@@ -2248,13 +2248,13 @@
         <v>19.5846</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.6615</v>
+        <v>-0.9792000000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>-3.0672</v>
+        <v>-3.0671</v>
       </c>
       <c r="U23" t="n">
-        <v>1.4058</v>
+        <v>2.0878</v>
       </c>
       <c r="V23" t="n">
         <v>11.1795</v>
